--- a/Assets/Resources/DataFiles/EnemyData/ExcelFile/EnemyDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/EnemyData/ExcelFile/EnemyDataLabel.xlsx
@@ -9,6 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KOR" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENG" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JPN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CHN" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30,12 +32,17 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -50,10 +57,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -567,4 +580,160 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>enemyId</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>enemyName</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>enemy.normal.ranged.patrol_drone</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>偵察ドローン</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>enemy.advanced.melee.working_machine</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>作業機械</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>enemy.elite.melee.excavator</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ショベルカー</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>enemy.boss.badass_mecha_mk1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Badass Mecha MK 1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>enemyId</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>enemyName</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>enemy.normal.ranged.patrol_drone</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>侦察无人机</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>enemy.advanced.melee.working_machine</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>作业机械</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>enemy.elite.melee.excavator</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>挖掘机</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>enemy.boss.badass_mecha_mk1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Badass Mecha MK 1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>